--- a/static/goalSchedule_results.xlsx
+++ b/static/goalSchedule_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,242 +450,502 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D2" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="E2" t="n">
-        <v>1699</v>
+        <v>990000</v>
       </c>
       <c r="F2" t="n">
-        <v>1699</v>
+        <v>990000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1398</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1404</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D3" t="n">
-        <v>1008</v>
+        <v>1001597</v>
       </c>
       <c r="E3" t="n">
-        <v>2398</v>
+        <v>990000</v>
       </c>
       <c r="F3" t="n">
-        <v>2412</v>
+        <v>1001597</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2097</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2115</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D4" t="n">
-        <v>1016</v>
+        <v>1013330</v>
       </c>
       <c r="E4" t="n">
-        <v>3097</v>
+        <v>990000</v>
       </c>
       <c r="F4" t="n">
-        <v>3131</v>
+        <v>1013330</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2796</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>2832</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D5" t="n">
-        <v>1024</v>
+        <v>1025201</v>
       </c>
       <c r="E5" t="n">
-        <v>3796</v>
+        <v>990000</v>
       </c>
       <c r="F5" t="n">
-        <v>3856</v>
+        <v>1025201</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3495</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>3556</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D6" t="n">
-        <v>1032</v>
+        <v>1037211</v>
       </c>
       <c r="E6" t="n">
-        <v>4495</v>
+        <v>990000</v>
       </c>
       <c r="F6" t="n">
-        <v>4588</v>
+        <v>1037211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4194</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>4286</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D7" t="n">
-        <v>1041</v>
+        <v>1049361</v>
       </c>
       <c r="E7" t="n">
-        <v>5194</v>
+        <v>990000</v>
       </c>
       <c r="F7" t="n">
-        <v>5327</v>
+        <v>1049361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4893</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>5022</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D8" t="n">
-        <v>1050</v>
+        <v>1061654</v>
       </c>
       <c r="E8" t="n">
-        <v>5893</v>
+        <v>990000</v>
       </c>
       <c r="F8" t="n">
-        <v>6072</v>
+        <v>1061654</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5592</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>5765</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D9" t="n">
-        <v>1059</v>
+        <v>1074091</v>
       </c>
       <c r="E9" t="n">
-        <v>6592</v>
+        <v>990000</v>
       </c>
       <c r="F9" t="n">
-        <v>6824</v>
+        <v>1074091</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6291</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>6514</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D10" t="n">
-        <v>1068</v>
+        <v>1086673</v>
       </c>
       <c r="E10" t="n">
-        <v>7291</v>
+        <v>990000</v>
       </c>
       <c r="F10" t="n">
-        <v>7582</v>
+        <v>1086673</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6990</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>7270</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D11" t="n">
-        <v>1077</v>
+        <v>1099403</v>
       </c>
       <c r="E11" t="n">
-        <v>7990</v>
+        <v>990000</v>
       </c>
       <c r="F11" t="n">
-        <v>8347</v>
+        <v>1099403</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7689</v>
+        <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>8033</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D12" t="n">
-        <v>1086</v>
+        <v>1112282</v>
       </c>
       <c r="E12" t="n">
-        <v>8689</v>
+        <v>990000</v>
       </c>
       <c r="F12" t="n">
-        <v>9119</v>
+        <v>1112282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>8388</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>8802</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1000</v>
+        <v>990000</v>
       </c>
       <c r="D13" t="n">
-        <v>1095</v>
+        <v>1125312</v>
       </c>
       <c r="E13" t="n">
-        <v>9388</v>
+        <v>990000</v>
       </c>
       <c r="F13" t="n">
-        <v>9897</v>
+        <v>1125312</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1138494</v>
+      </c>
+      <c r="E14" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1138494</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1151831</v>
+      </c>
+      <c r="E15" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1151831</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1165324</v>
+      </c>
+      <c r="E16" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1165324</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1178975</v>
+      </c>
+      <c r="E17" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1178975</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1192786</v>
+      </c>
+      <c r="E18" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1192786</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1206759</v>
+      </c>
+      <c r="E19" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1206759</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1220896</v>
+      </c>
+      <c r="E20" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1220896</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1235198</v>
+      </c>
+      <c r="E21" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1235198</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1249668</v>
+      </c>
+      <c r="E22" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1249668</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1264307</v>
+      </c>
+      <c r="E23" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1264307</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1279118</v>
+      </c>
+      <c r="E24" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1279118</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1294102</v>
+      </c>
+      <c r="E25" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1294102</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1309262</v>
+      </c>
+      <c r="E26" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1309262</v>
       </c>
     </row>
   </sheetData>

--- a/static/goalSchedule_results.xlsx
+++ b/static/goalSchedule_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,502 +450,262 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="C2" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D2" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="E2" t="n">
-        <v>990000</v>
+        <v>1699</v>
       </c>
       <c r="F2" t="n">
-        <v>990000</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1398</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1404</v>
       </c>
       <c r="C3" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D3" t="n">
-        <v>1001597</v>
+        <v>1008</v>
       </c>
       <c r="E3" t="n">
-        <v>990000</v>
+        <v>2398</v>
       </c>
       <c r="F3" t="n">
-        <v>1001597</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>2097</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="C4" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D4" t="n">
-        <v>1013330</v>
+        <v>1016</v>
       </c>
       <c r="E4" t="n">
-        <v>990000</v>
+        <v>3097</v>
       </c>
       <c r="F4" t="n">
-        <v>1013330</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>2796</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2832</v>
       </c>
       <c r="C5" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D5" t="n">
-        <v>1025201</v>
+        <v>1024</v>
       </c>
       <c r="E5" t="n">
-        <v>990000</v>
+        <v>3796</v>
       </c>
       <c r="F5" t="n">
-        <v>1025201</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>3495</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>3556</v>
       </c>
       <c r="C6" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D6" t="n">
-        <v>1037211</v>
+        <v>1032</v>
       </c>
       <c r="E6" t="n">
-        <v>990000</v>
+        <v>4495</v>
       </c>
       <c r="F6" t="n">
-        <v>1037211</v>
+        <v>4588</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>4194</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>4286</v>
       </c>
       <c r="C7" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D7" t="n">
-        <v>1049361</v>
+        <v>1041</v>
       </c>
       <c r="E7" t="n">
-        <v>990000</v>
+        <v>5194</v>
       </c>
       <c r="F7" t="n">
-        <v>1049361</v>
+        <v>5327</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>4893</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>5022</v>
       </c>
       <c r="C8" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D8" t="n">
-        <v>1061654</v>
+        <v>1050</v>
       </c>
       <c r="E8" t="n">
-        <v>990000</v>
+        <v>5893</v>
       </c>
       <c r="F8" t="n">
-        <v>1061654</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>5592</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>5765</v>
       </c>
       <c r="C9" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D9" t="n">
-        <v>1074091</v>
+        <v>1059</v>
       </c>
       <c r="E9" t="n">
-        <v>990000</v>
+        <v>6592</v>
       </c>
       <c r="F9" t="n">
-        <v>1074091</v>
+        <v>6824</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>6291</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6514</v>
       </c>
       <c r="C10" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D10" t="n">
-        <v>1086673</v>
+        <v>1068</v>
       </c>
       <c r="E10" t="n">
-        <v>990000</v>
+        <v>7291</v>
       </c>
       <c r="F10" t="n">
-        <v>1086673</v>
+        <v>7582</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>6990</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>7270</v>
       </c>
       <c r="C11" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D11" t="n">
-        <v>1099403</v>
+        <v>1077</v>
       </c>
       <c r="E11" t="n">
-        <v>990000</v>
+        <v>7990</v>
       </c>
       <c r="F11" t="n">
-        <v>1099403</v>
+        <v>8347</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>7689</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>8033</v>
       </c>
       <c r="C12" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D12" t="n">
-        <v>1112282</v>
+        <v>1086</v>
       </c>
       <c r="E12" t="n">
-        <v>990000</v>
+        <v>8689</v>
       </c>
       <c r="F12" t="n">
-        <v>1112282</v>
+        <v>9119</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>8388</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>8802</v>
       </c>
       <c r="C13" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D13" t="n">
-        <v>1125312</v>
+        <v>1095</v>
       </c>
       <c r="E13" t="n">
-        <v>990000</v>
+        <v>9388</v>
       </c>
       <c r="F13" t="n">
-        <v>1125312</v>
+        <v>9897</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>8388</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>8879</v>
       </c>
       <c r="C14" t="n">
-        <v>990000</v>
+        <v>1000</v>
       </c>
       <c r="D14" t="n">
-        <v>1138494</v>
+        <v>1104</v>
       </c>
       <c r="E14" t="n">
-        <v>990000</v>
+        <v>9388</v>
       </c>
       <c r="F14" t="n">
-        <v>1138494</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>0</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1151831</v>
-      </c>
-      <c r="E15" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1151831</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>0</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1165324</v>
-      </c>
-      <c r="E16" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1165324</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>0</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1178975</v>
-      </c>
-      <c r="E17" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1178975</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>0</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1192786</v>
-      </c>
-      <c r="E18" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1192786</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1206759</v>
-      </c>
-      <c r="E19" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1206759</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1220896</v>
-      </c>
-      <c r="E20" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1220896</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1235198</v>
-      </c>
-      <c r="E21" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1235198</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1249668</v>
-      </c>
-      <c r="E22" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1249668</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>0</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1264307</v>
-      </c>
-      <c r="E23" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1264307</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1279118</v>
-      </c>
-      <c r="E24" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1279118</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>0</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1294102</v>
-      </c>
-      <c r="E25" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1294102</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>990000</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1309262</v>
-      </c>
-      <c r="E26" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1309262</v>
+        <v>9983</v>
       </c>
     </row>
   </sheetData>
